--- a/MGT_2026_Master.xlsx
+++ b/MGT_2026_Master.xlsx
@@ -11,14 +11,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F5" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gross_Historial" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medal_Calc" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medal_Fechas" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medal_Consolidado" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixture" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jugadores" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F6" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gross_Historial" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medal_Calc" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medal_Fechas" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medal_Consolidado" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixture" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jugadores" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -2191,6 +2192,681 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="24" customWidth="1" style="21" min="1" max="1"/>
+    <col width="8" customWidth="1" style="21" min="2" max="2"/>
+    <col width="11" customWidth="1" style="21" min="3" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21.75" customHeight="1" s="22">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="inlineStr">
+        <is>
+          <t>F1 Pts</t>
+        </is>
+      </c>
+      <c r="D1" s="27" t="inlineStr">
+        <is>
+          <t>F2 Pts</t>
+        </is>
+      </c>
+      <c r="E1" s="27" t="inlineStr">
+        <is>
+          <t>F3 Pts</t>
+        </is>
+      </c>
+      <c r="F1" s="21" t="inlineStr">
+        <is>
+          <t>F5 Pts</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>F6 Pts</t>
+        </is>
+      </c>
+      <c r="H1" s="21" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="22">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Fernandez, Lucas</t>
+        </is>
+      </c>
+      <c r="B2" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C2" s="29">
+        <f>IFERROR(VLOOKUP(A2, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D2" s="29">
+        <f>IFERROR(VLOOKUP(A2, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E2" s="29">
+        <f>IFERROR(VLOOKUP(A2, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F2" s="21">
+        <f>IFERROR(VLOOKUP(A2, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G2" s="21">
+        <f>IFERROR(VLOOKUP(A2, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H2" s="21">
+        <f>SUM(C2:G2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="22">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Gatto, Mariano</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C3" s="29">
+        <f>IFERROR(VLOOKUP(A3, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D3" s="29">
+        <f>IFERROR(VLOOKUP(A3, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E3" s="29">
+        <f>IFERROR(VLOOKUP(A3, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F3" s="21">
+        <f>IFERROR(VLOOKUP(A3, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G3" s="21">
+        <f>IFERROR(VLOOKUP(A3, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H3" s="21">
+        <f>SUM(C3:G3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="22">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>Guevara, Franki</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C4" s="29">
+        <f>IFERROR(VLOOKUP(A4, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D4" s="29">
+        <f>IFERROR(VLOOKUP(A4, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E4" s="29">
+        <f>IFERROR(VLOOKUP(A4, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F4" s="21">
+        <f>IFERROR(VLOOKUP(A4, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="21">
+        <f>IFERROR(VLOOKUP(A4, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H4" s="21">
+        <f>SUM(C4:G4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="22">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Vogelius, Nico</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C5" s="29">
+        <f>IFERROR(VLOOKUP(A5, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="29">
+        <f>IFERROR(VLOOKUP(A5, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E5" s="29">
+        <f>IFERROR(VLOOKUP(A5, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F5" s="21">
+        <f>IFERROR(VLOOKUP(A5, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="21">
+        <f>IFERROR(VLOOKUP(A5, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H5" s="21">
+        <f>SUM(C5:G5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="22">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Elizalde, Juancho</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C6" s="29">
+        <f>IFERROR(VLOOKUP(A6, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="29">
+        <f>IFERROR(VLOOKUP(A6, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E6" s="29">
+        <f>IFERROR(VLOOKUP(A6, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="21">
+        <f>IFERROR(VLOOKUP(A6, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="21">
+        <f>IFERROR(VLOOKUP(A6, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="21">
+        <f>SUM(C6:G6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="22">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Tarasido, Gonzalo</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C7" s="29">
+        <f>IFERROR(VLOOKUP(A7, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="29">
+        <f>IFERROR(VLOOKUP(A7, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E7" s="29">
+        <f>IFERROR(VLOOKUP(A7, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="21">
+        <f>IFERROR(VLOOKUP(A7, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="21">
+        <f>IFERROR(VLOOKUP(A7, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="21">
+        <f>SUM(C7:G7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="22">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Pannullo, Tincho</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C8" s="29">
+        <f>IFERROR(VLOOKUP(A8, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="29">
+        <f>IFERROR(VLOOKUP(A8, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E8" s="29">
+        <f>IFERROR(VLOOKUP(A8, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="21">
+        <f>IFERROR(VLOOKUP(A8, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="21">
+        <f>IFERROR(VLOOKUP(A8, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="21">
+        <f>SUM(C8:G8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="22">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Molinario, Andy</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C9" s="29">
+        <f>IFERROR(VLOOKUP(A9, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="29">
+        <f>IFERROR(VLOOKUP(A9, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E9" s="29">
+        <f>IFERROR(VLOOKUP(A9, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="21">
+        <f>IFERROR(VLOOKUP(A9, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="21">
+        <f>IFERROR(VLOOKUP(A9, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="21">
+        <f>SUM(C9:G9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="22">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Mendez, Pato</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C10" s="29">
+        <f>IFERROR(VLOOKUP(A10, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="29">
+        <f>IFERROR(VLOOKUP(A10, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E10" s="29">
+        <f>IFERROR(VLOOKUP(A10, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="21">
+        <f>IFERROR(VLOOKUP(A10, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="21">
+        <f>IFERROR(VLOOKUP(A10, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="21">
+        <f>SUM(C10:G10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="22">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Dipaola, Martin</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C11" s="29">
+        <f>IFERROR(VLOOKUP(A11, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="29">
+        <f>IFERROR(VLOOKUP(A11, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E11" s="29">
+        <f>IFERROR(VLOOKUP(A11, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="21">
+        <f>IFERROR(VLOOKUP(A11, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="21">
+        <f>IFERROR(VLOOKUP(A11, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="21">
+        <f>SUM(C11:G11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="22">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Benegas, Pancho</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C12" s="29">
+        <f>IFERROR(VLOOKUP(A12, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="29">
+        <f>IFERROR(VLOOKUP(A12, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E12" s="29">
+        <f>IFERROR(VLOOKUP(A12, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F12" s="21">
+        <f>IFERROR(VLOOKUP(A12, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="21">
+        <f>IFERROR(VLOOKUP(A12, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="21">
+        <f>SUM(C12:G12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="22">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>Canónico, Agus</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C13" s="29">
+        <f>IFERROR(VLOOKUP(A13, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="29">
+        <f>IFERROR(VLOOKUP(A13, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E13" s="29">
+        <f>IFERROR(VLOOKUP(A13, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>IFERROR(VLOOKUP(A13, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="21">
+        <f>IFERROR(VLOOKUP(A13, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="21">
+        <f>SUM(C13:G13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="22">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Basaldua, Ignacio</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C14" s="29">
+        <f>IFERROR(VLOOKUP(A14, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="29">
+        <f>IFERROR(VLOOKUP(A14, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E14" s="29">
+        <f>IFERROR(VLOOKUP(A14, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="21">
+        <f>IFERROR(VLOOKUP(A14, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="21">
+        <f>IFERROR(VLOOKUP(A14, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="21">
+        <f>SUM(C14:G14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="22">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>Zunino, Javi</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C15" s="29">
+        <f>IFERROR(VLOOKUP(A15, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="29">
+        <f>IFERROR(VLOOKUP(A15, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E15" s="29">
+        <f>IFERROR(VLOOKUP(A15, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="21">
+        <f>IFERROR(VLOOKUP(A15, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="21">
+        <f>IFERROR(VLOOKUP(A15, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="21">
+        <f>SUM(C15:G15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="22">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>Scapparone, Nico</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C16" s="29">
+        <f>IFERROR(VLOOKUP(A16, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="29">
+        <f>IFERROR(VLOOKUP(A16, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E16" s="29">
+        <f>IFERROR(VLOOKUP(A16, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="21">
+        <f>IFERROR(VLOOKUP(A16, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="21">
+        <f>IFERROR(VLOOKUP(A16, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="21">
+        <f>SUM(C16:G16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="22">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Gonzalez, Agus</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C17" s="29">
+        <f>IFERROR(VLOOKUP(A17, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="29">
+        <f>IFERROR(VLOOKUP(A17, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E17" s="29">
+        <f>IFERROR(VLOOKUP(A17, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="21">
+        <f>IFERROR(VLOOKUP(A17, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="21">
+        <f>IFERROR(VLOOKUP(A17, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="21">
+        <f>SUM(C17:G17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="22">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>Gatto, Alejandro</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" s="32">
+        <f>IFERROR(VLOOKUP(A18, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="32">
+        <f>IFERROR(VLOOKUP(A18, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="E18" s="32">
+        <f>IFERROR(VLOOKUP(A18, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="F18" s="21">
+        <f>IFERROR(VLOOKUP(A18, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="21">
+        <f>IFERROR(VLOOKUP(A18, Medal_Fechas!$A:$Q, 17, FALSE()), 0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="21">
+        <f>SUM(C18:G18)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
@@ -2420,7 +3096,7 @@
       </c>
       <c r="B7" s="28" t="inlineStr">
         <is>
-          <t>01-Ago-2026</t>
+          <t>08-Ago-2026</t>
         </is>
       </c>
       <c r="C7" s="28" t="inlineStr">
@@ -2430,7 +3106,7 @@
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>Fourball 2v2</t>
+          <t>Individual 1v1</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
@@ -2440,12 +3116,12 @@
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>Dipaola + Canónico</t>
+          <t>Guevara + Vogelius</t>
         </is>
       </c>
       <c r="G7" s="32" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Jugada</t>
         </is>
       </c>
     </row>
@@ -2455,7 +3131,7 @@
       </c>
       <c r="B8" s="28" t="inlineStr">
         <is>
-          <t>05-Sep-2026</t>
+          <t>12-Sep-2026</t>
         </is>
       </c>
       <c r="C8" s="28" t="inlineStr">
@@ -2465,7 +3141,7 @@
       </c>
       <c r="D8" s="28" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>Fourball 2v2</t>
         </is>
       </c>
       <c r="E8" s="28" t="inlineStr">
@@ -2475,7 +3151,7 @@
       </c>
       <c r="F8" s="28" t="inlineStr">
         <is>
-          <t>Vogelius + Mendez</t>
+          <t>Scapparone + Benegas</t>
         </is>
       </c>
       <c r="G8" s="32" t="inlineStr">
@@ -2500,7 +3176,7 @@
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>Fourball 2v2</t>
+          <t>Individual 1v1</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
@@ -2510,7 +3186,7 @@
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>Molinario + Scapparone</t>
+          <t>Elizalde + Mendez</t>
         </is>
       </c>
       <c r="G9" s="32" t="inlineStr">
@@ -2525,7 +3201,7 @@
       </c>
       <c r="B10" s="28" t="inlineStr">
         <is>
-          <t>07-Nov-2026</t>
+          <t>04-Nov-2026</t>
         </is>
       </c>
       <c r="C10" s="28" t="inlineStr">
@@ -2545,7 +3221,7 @@
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
-          <t>Elizalde + Fernandez</t>
+          <t>GIRA</t>
         </is>
       </c>
       <c r="G10" s="32" t="inlineStr">
@@ -2560,7 +3236,7 @@
       </c>
       <c r="B11" s="28" t="inlineStr">
         <is>
-          <t>28-Nov-2026</t>
+          <t>09-Nov-2026</t>
         </is>
       </c>
       <c r="C11" s="28" t="inlineStr">
@@ -2570,7 +3246,7 @@
       </c>
       <c r="D11" s="28" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>Individual 1v1</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
@@ -2580,7 +3256,7 @@
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>La Comisión</t>
+          <t>GIRA</t>
         </is>
       </c>
       <c r="G11" s="32" t="inlineStr">
@@ -2596,7 +3272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5815,7 +6491,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10656,6 +11332,1476 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
+  <dimension ref="A1:X23"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="22" customWidth="1" style="21" min="1" max="1"/>
+    <col width="8" customWidth="1" style="21" min="2" max="2"/>
+    <col width="5" customWidth="1" style="21" min="3" max="3"/>
+    <col width="8" customWidth="1" style="21" min="21" max="21"/>
+    <col width="9" customWidth="1" style="21" min="22" max="22"/>
+    <col width="10" customWidth="1" style="21" min="23" max="23"/>
+    <col width="7" customWidth="1" style="21" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17.35" customHeight="1" s="22">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>FECHA 6 — 08 Ago 2026 — CUBA Fátima</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="22">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Par 72 | Individual 1v1 | Organizadores: Guevara + Vogelius</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="22">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>HCP</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>cancha</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="H5" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="J5" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="K5" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="M5" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="N5" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="P5" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q5" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="S5" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="T5" s="25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="22">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>PAR</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" s="26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="22">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Jugador</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="G7" s="27" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="H7" s="27" t="inlineStr">
+        <is>
+          <t>H6</t>
+        </is>
+      </c>
+      <c r="I7" s="27" t="inlineStr">
+        <is>
+          <t>H7</t>
+        </is>
+      </c>
+      <c r="J7" s="27" t="inlineStr">
+        <is>
+          <t>H8</t>
+        </is>
+      </c>
+      <c r="K7" s="27" t="inlineStr">
+        <is>
+          <t>H9</t>
+        </is>
+      </c>
+      <c r="L7" s="27" t="inlineStr">
+        <is>
+          <t>H10</t>
+        </is>
+      </c>
+      <c r="M7" s="27" t="inlineStr">
+        <is>
+          <t>H11</t>
+        </is>
+      </c>
+      <c r="N7" s="27" t="inlineStr">
+        <is>
+          <t>H12</t>
+        </is>
+      </c>
+      <c r="O7" s="27" t="inlineStr">
+        <is>
+          <t>H13</t>
+        </is>
+      </c>
+      <c r="P7" s="27" t="inlineStr">
+        <is>
+          <t>H14</t>
+        </is>
+      </c>
+      <c r="Q7" s="27" t="inlineStr">
+        <is>
+          <t>H15</t>
+        </is>
+      </c>
+      <c r="R7" s="27" t="inlineStr">
+        <is>
+          <t>H16</t>
+        </is>
+      </c>
+      <c r="S7" s="27" t="inlineStr">
+        <is>
+          <t>H17</t>
+        </is>
+      </c>
+      <c r="T7" s="27" t="inlineStr">
+        <is>
+          <t>H18</t>
+        </is>
+      </c>
+      <c r="U7" s="27" t="inlineStr">
+        <is>
+          <t>Gross</t>
+        </is>
+      </c>
+      <c r="V7" s="27" t="inlineStr">
+        <is>
+          <t>Hdcp día</t>
+        </is>
+      </c>
+      <c r="W7" s="27" t="inlineStr">
+        <is>
+          <t>Hdcp aplic</t>
+        </is>
+      </c>
+      <c r="X7" s="27" t="inlineStr">
+        <is>
+          <t>Neto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="22">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Gonzalez, Agus</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O8" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" s="28">
+        <f>IF(COUNT(C8:T8)=18,SUM(C8:T8),"")</f>
+        <v/>
+      </c>
+      <c r="V8" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="W8" s="28">
+        <f>IF(V8="","",MIN(V8,26))</f>
+        <v/>
+      </c>
+      <c r="X8" s="28">
+        <f>IF(OR(U8="",W8=""),"",U8-W8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="22">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Tarasido, Gonzalo</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="O9" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" s="28">
+        <f>IF(COUNT(C9:T9)=18,SUM(C9:T9),"")</f>
+        <v/>
+      </c>
+      <c r="V9" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="W9" s="28">
+        <f>IF(V9="","",MIN(V9,26))</f>
+        <v/>
+      </c>
+      <c r="X9" s="28">
+        <f>IF(OR(U9="",W9=""),"",U9-W9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="22">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Zunino, Javi</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="29" t="n"/>
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="29" t="n"/>
+      <c r="G10" s="29" t="n"/>
+      <c r="H10" s="29" t="n"/>
+      <c r="I10" s="29" t="n"/>
+      <c r="J10" s="29" t="n"/>
+      <c r="K10" s="29" t="n"/>
+      <c r="L10" s="29" t="n"/>
+      <c r="M10" s="29" t="n"/>
+      <c r="N10" s="29" t="n"/>
+      <c r="O10" s="29" t="n"/>
+      <c r="P10" s="29" t="n"/>
+      <c r="Q10" s="29" t="n"/>
+      <c r="R10" s="29" t="n"/>
+      <c r="S10" s="29" t="n"/>
+      <c r="T10" s="29" t="n"/>
+      <c r="U10" s="28">
+        <f>IF(COUNT(C10:T10)=18,SUM(C10:T10),"")</f>
+        <v/>
+      </c>
+      <c r="V10" s="28" t="n"/>
+      <c r="W10" s="28">
+        <f>IF(V10="","",MIN(V10,26))</f>
+        <v/>
+      </c>
+      <c r="X10" s="28">
+        <f>IF(OR(U10="",W10=""),"",U10-W10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="22">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>Basaldua, Ignacio</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="N11" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" s="28">
+        <f>IF(COUNT(C11:T11)=18,SUM(C11:T11),"")</f>
+        <v/>
+      </c>
+      <c r="V11" s="28" t="n">
+        <v>17</v>
+      </c>
+      <c r="W11" s="28">
+        <f>IF(V11="","",MIN(V11,26))</f>
+        <v/>
+      </c>
+      <c r="X11" s="28">
+        <f>IF(OR(U11="",W11=""),"",U11-W11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="22">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>Pannullo, Tincho</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M12" s="29" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O12" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" s="28">
+        <f>IF(COUNT(C12:T12)=18,SUM(C12:T12),"")</f>
+        <v/>
+      </c>
+      <c r="V12" s="28" t="n">
+        <v>17</v>
+      </c>
+      <c r="W12" s="28">
+        <f>IF(V12="","",MIN(V12,26))</f>
+        <v/>
+      </c>
+      <c r="X12" s="28">
+        <f>IF(OR(U12="",W12=""),"",U12-W12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="22">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>Benegas, Pancho</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O13" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q13" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="U13" s="28">
+        <f>IF(COUNT(C13:T13)=18,SUM(C13:T13),"")</f>
+        <v/>
+      </c>
+      <c r="V13" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="W13" s="28">
+        <f>IF(V13="","",MIN(V13,26))</f>
+        <v/>
+      </c>
+      <c r="X13" s="28">
+        <f>IF(OR(U13="",W13=""),"",U13-W13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="22">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Guevara, Franki</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O14" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="R14" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" s="28">
+        <f>IF(COUNT(C14:T14)=18,SUM(C14:T14),"")</f>
+        <v/>
+      </c>
+      <c r="V14" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="W14" s="28">
+        <f>IF(V14="","",MIN(V14,26))</f>
+        <v/>
+      </c>
+      <c r="X14" s="28">
+        <f>IF(OR(U14="",W14=""),"",U14-W14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="22">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>Dipaola, Martin</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>GRIS</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O15" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="P15" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" s="28">
+        <f>IF(COUNT(C15:T15)=18,SUM(C15:T15),"")</f>
+        <v/>
+      </c>
+      <c r="V15" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="W15" s="28">
+        <f>IF(V15="","",MIN(V15,26))</f>
+        <v/>
+      </c>
+      <c r="X15" s="28">
+        <f>IF(OR(U15="",W15=""),"",U15-W15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="22">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>Gatto, Mariano</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="29" t="n"/>
+      <c r="G16" s="29" t="n"/>
+      <c r="H16" s="29" t="n"/>
+      <c r="I16" s="29" t="n"/>
+      <c r="J16" s="29" t="n"/>
+      <c r="K16" s="29" t="n"/>
+      <c r="L16" s="29" t="n"/>
+      <c r="M16" s="29" t="n"/>
+      <c r="N16" s="29" t="n"/>
+      <c r="O16" s="29" t="n"/>
+      <c r="P16" s="29" t="n"/>
+      <c r="Q16" s="29" t="n"/>
+      <c r="R16" s="29" t="n"/>
+      <c r="S16" s="29" t="n"/>
+      <c r="T16" s="29" t="n"/>
+      <c r="U16" s="28">
+        <f>IF(COUNT(C16:T16)=18,SUM(C16:T16),"")</f>
+        <v/>
+      </c>
+      <c r="V16" s="28" t="n"/>
+      <c r="W16" s="28">
+        <f>IF(V16="","",MIN(V16,26))</f>
+        <v/>
+      </c>
+      <c r="X16" s="28">
+        <f>IF(OR(U16="",W16=""),"",U16-W16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="22">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Elizalde, Juancho</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="N17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="P17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" s="28">
+        <f>IF(COUNT(C17:T17)=18,SUM(C17:T17),"")</f>
+        <v/>
+      </c>
+      <c r="V17" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="W17" s="28">
+        <f>IF(V17="","",MIN(V17,26))</f>
+        <v/>
+      </c>
+      <c r="X17" s="28">
+        <f>IF(OR(U17="",W17=""),"",U17-W17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="22">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Canónico, Agus</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M18" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="N18" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="O18" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="P18" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" s="28">
+        <f>IF(COUNT(C18:T18)=18,SUM(C18:T18),"")</f>
+        <v/>
+      </c>
+      <c r="V18" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="W18" s="28">
+        <f>IF(V18="","",MIN(V18,26))</f>
+        <v/>
+      </c>
+      <c r="X18" s="28">
+        <f>IF(OR(U18="",W18=""),"",U18-W18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="22">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>Vogelius, Nico</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="I19" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="N19" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O19" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="R19" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="U19" s="28">
+        <f>IF(COUNT(C19:T19)=18,SUM(C19:T19),"")</f>
+        <v/>
+      </c>
+      <c r="V19" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="W19" s="28">
+        <f>IF(V19="","",MIN(V19,26))</f>
+        <v/>
+      </c>
+      <c r="X19" s="28">
+        <f>IF(OR(U19="",W19=""),"",U19-W19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="22">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>Mendez, Pato</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="N20" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="P20" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="R20" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" s="28">
+        <f>IF(COUNT(C20:T20)=18,SUM(C20:T20),"")</f>
+        <v/>
+      </c>
+      <c r="V20" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="W20" s="28">
+        <f>IF(V20="","",MIN(V20,26))</f>
+        <v/>
+      </c>
+      <c r="X20" s="28">
+        <f>IF(OR(U20="",W20=""),"",U20-W20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="22">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>Molinario, Andy</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="N21" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="O21" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="P21" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="R21" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="U21" s="28">
+        <f>IF(COUNT(C21:T21)=18,SUM(C21:T21),"")</f>
+        <v/>
+      </c>
+      <c r="V21" s="28" t="n">
+        <v>17</v>
+      </c>
+      <c r="W21" s="28">
+        <f>IF(V21="","",MIN(V21,26))</f>
+        <v/>
+      </c>
+      <c r="X21" s="28">
+        <f>IF(OR(U21="",W21=""),"",U21-W21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="22">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>Scapparone, Nico</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="29" t="n"/>
+      <c r="G22" s="29" t="n"/>
+      <c r="H22" s="29" t="n"/>
+      <c r="I22" s="29" t="n"/>
+      <c r="J22" s="29" t="n"/>
+      <c r="K22" s="29" t="n"/>
+      <c r="L22" s="29" t="n"/>
+      <c r="M22" s="29" t="n"/>
+      <c r="N22" s="29" t="n"/>
+      <c r="O22" s="29" t="n"/>
+      <c r="P22" s="29" t="n"/>
+      <c r="Q22" s="29" t="n"/>
+      <c r="R22" s="29" t="n"/>
+      <c r="S22" s="29" t="n"/>
+      <c r="T22" s="29" t="n"/>
+      <c r="U22" s="28">
+        <f>IF(COUNT(C22:T22)=18,SUM(C22:T22),"")</f>
+        <v/>
+      </c>
+      <c r="V22" s="28" t="n"/>
+      <c r="W22" s="28">
+        <f>IF(V22="","",MIN(V22,26))</f>
+        <v/>
+      </c>
+      <c r="X22" s="28">
+        <f>IF(OR(U22="",W22=""),"",U22-W22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="22">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>Fernandez, Lucas</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="inlineStr">
+        <is>
+          <t>ROJO</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H23" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="I23" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="L23" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="M23" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="N23" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O23" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="P23" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="R23" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="U23" s="28">
+        <f>IF(COUNT(C23:T23)=18,SUM(C23:T23),"")</f>
+        <v/>
+      </c>
+      <c r="V23" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="W23" s="28">
+        <f>IF(V23="","",MIN(V23,26))</f>
+        <v/>
+      </c>
+      <c r="X23" s="28">
+        <f>IF(OR(U23="",W23=""),"",U23-W23)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <dimension ref="A1:V67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
@@ -10737,12 +12883,22 @@
           <t>F5 Dif</t>
         </is>
       </c>
-      <c r="M2" s="27" t="inlineStr">
+      <c r="M2" s="21" t="inlineStr">
+        <is>
+          <t>F6 Pts</t>
+        </is>
+      </c>
+      <c r="N2" s="21" t="inlineStr">
+        <is>
+          <t>F6 Dif</t>
+        </is>
+      </c>
+      <c r="O2" s="21" t="inlineStr">
         <is>
           <t>TOT Pts</t>
         </is>
       </c>
-      <c r="N2" s="27" t="inlineStr">
+      <c r="P2" s="21" t="inlineStr">
         <is>
           <t>TOT Dif</t>
         </is>
@@ -10779,12 +12935,18 @@
       <c r="L3" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="M3" s="29">
-        <f>SUM(C3,E3,G3,I3,K3)</f>
-        <v/>
-      </c>
-      <c r="N3" s="29">
-        <f>SUM(D3,F3,H3,J3,L3)</f>
+      <c r="M3" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" s="21">
+        <f>SUM(C3,E3,G3,I3,K3,M3)</f>
+        <v/>
+      </c>
+      <c r="P3" s="21">
+        <f>SUM(D3,F3,H3,J3,L3,N3)</f>
         <v/>
       </c>
     </row>
@@ -10829,12 +12991,18 @@
       <c r="L4" s="21" t="n">
         <v>-4</v>
       </c>
-      <c r="M4" s="29">
-        <f>SUM(C4,E4,G4,I4,K4)</f>
-        <v/>
-      </c>
-      <c r="N4" s="29">
-        <f>SUM(D4,F4,H4,J4,L4)</f>
+      <c r="M4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="21" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O4" s="21">
+        <f>SUM(C4,E4,G4,I4,K4,M4)</f>
+        <v/>
+      </c>
+      <c r="P4" s="21">
+        <f>SUM(D4,F4,H4,J4,L4,N4)</f>
         <v/>
       </c>
     </row>
@@ -10865,12 +13033,18 @@
       <c r="L5" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="29">
-        <f>SUM(C5,E5,G5,I5,K5)</f>
-        <v/>
-      </c>
-      <c r="N5" s="29">
-        <f>SUM(D5,F5,H5,J5,L5)</f>
+      <c r="M5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="21">
+        <f>SUM(C5,E5,G5,I5,K5,M5)</f>
+        <v/>
+      </c>
+      <c r="P5" s="21">
+        <f>SUM(D5,F5,H5,J5,L5,N5)</f>
         <v/>
       </c>
     </row>
@@ -10905,12 +13079,18 @@
       <c r="L6" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="29">
-        <f>SUM(C6,E6,G6,I6,K6)</f>
-        <v/>
-      </c>
-      <c r="N6" s="29">
-        <f>SUM(D6,F6,H6,J6,L6)</f>
+      <c r="M6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="21" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O6" s="21">
+        <f>SUM(C6,E6,G6,I6,K6,M6)</f>
+        <v/>
+      </c>
+      <c r="P6" s="21">
+        <f>SUM(D6,F6,H6,J6,L6,N6)</f>
         <v/>
       </c>
     </row>
@@ -10949,12 +13129,18 @@
       <c r="J7" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="29">
-        <f>SUM(C7,E7,G7,I7,K7)</f>
-        <v/>
-      </c>
-      <c r="N7" s="29">
-        <f>SUM(D7,F7,H7,J7,L7)</f>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7">
+        <f>SUM(C7,E7,G7,I7,K7,M7)</f>
+        <v/>
+      </c>
+      <c r="P7">
+        <f>SUM(D7,F7,H7,J7,L7,N7)</f>
         <v/>
       </c>
     </row>
@@ -10999,12 +13185,18 @@
       <c r="L8" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="M8" s="29">
-        <f>SUM(C8,E8,G8,I8,K8)</f>
-        <v/>
-      </c>
-      <c r="N8" s="29">
-        <f>SUM(D8,F8,H8,J8,L8)</f>
+      <c r="M8" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" s="21">
+        <f>SUM(C8,E8,G8,I8,K8,M8)</f>
+        <v/>
+      </c>
+      <c r="P8" s="21">
+        <f>SUM(D8,F8,H8,J8,L8,N8)</f>
         <v/>
       </c>
     </row>
@@ -11049,12 +13241,18 @@
       <c r="L9" s="21" t="n">
         <v>-4</v>
       </c>
-      <c r="M9" s="29">
-        <f>SUM(C9,E9,G9,I9,K9)</f>
-        <v/>
-      </c>
-      <c r="N9" s="29">
-        <f>SUM(D9,F9,H9,J9,L9)</f>
+      <c r="M9" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" s="21">
+        <f>SUM(C9,E9,G9,I9,K9,M9)</f>
+        <v/>
+      </c>
+      <c r="P9" s="21">
+        <f>SUM(D9,F9,H9,J9,L9,N9)</f>
         <v/>
       </c>
     </row>
@@ -11099,12 +13297,18 @@
       <c r="L10" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="M10" s="29">
-        <f>SUM(C10,E10,G10,I10,K10)</f>
-        <v/>
-      </c>
-      <c r="N10" s="29">
-        <f>SUM(D10,F10,H10,J10,L10)</f>
+      <c r="M10" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="21">
+        <f>SUM(C10,E10,G10,I10,K10,M10)</f>
+        <v/>
+      </c>
+      <c r="P10" s="21">
+        <f>SUM(D10,F10,H10,J10,L10,N10)</f>
         <v/>
       </c>
     </row>
@@ -11149,12 +13353,18 @@
       <c r="L11" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="M11" s="29">
-        <f>SUM(C11,E11,G11,I11,K11)</f>
-        <v/>
-      </c>
-      <c r="N11" s="29">
-        <f>SUM(D11,F11,H11,J11,L11)</f>
+      <c r="M11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="21" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O11" s="21">
+        <f>SUM(C11,E11,G11,I11,K11,M11)</f>
+        <v/>
+      </c>
+      <c r="P11" s="21">
+        <f>SUM(D11,F11,H11,J11,L11,N11)</f>
         <v/>
       </c>
     </row>
@@ -11199,12 +13409,18 @@
       <c r="L12" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="M12" s="29">
-        <f>SUM(C12,E12,G12,I12,K12)</f>
-        <v/>
-      </c>
-      <c r="N12" s="29">
-        <f>SUM(D12,F12,H12,J12,L12)</f>
+      <c r="M12" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="21">
+        <f>SUM(C12,E12,G12,I12,K12,M12)</f>
+        <v/>
+      </c>
+      <c r="P12" s="21">
+        <f>SUM(D12,F12,H12,J12,L12,N12)</f>
         <v/>
       </c>
     </row>
@@ -11249,12 +13465,18 @@
       <c r="L13" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="29">
-        <f>SUM(C13,E13,G13,I13,K13)</f>
-        <v/>
-      </c>
-      <c r="N13" s="29">
-        <f>SUM(D13,F13,H13,J13,L13)</f>
+      <c r="M13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="21" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O13" s="21">
+        <f>SUM(C13,E13,G13,I13,K13,M13)</f>
+        <v/>
+      </c>
+      <c r="P13" s="21">
+        <f>SUM(D13,F13,H13,J13,L13,N13)</f>
         <v/>
       </c>
     </row>
@@ -11293,12 +13515,18 @@
       <c r="L14" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="29">
-        <f>SUM(C14,E14,G14,I14,K14)</f>
-        <v/>
-      </c>
-      <c r="N14" s="29">
-        <f>SUM(D14,F14,H14,J14,L14)</f>
+      <c r="M14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="21" t="n">
+        <v>-7</v>
+      </c>
+      <c r="O14" s="21">
+        <f>SUM(C14,E14,G14,I14,K14,M14)</f>
+        <v/>
+      </c>
+      <c r="P14" s="21">
+        <f>SUM(D14,F14,H14,J14,L14,N14)</f>
         <v/>
       </c>
     </row>
@@ -11343,12 +13571,18 @@
       <c r="L15" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="29">
-        <f>SUM(C15,E15,G15,I15,K15)</f>
-        <v/>
-      </c>
-      <c r="N15" s="29">
-        <f>SUM(D15,F15,H15,J15,L15)</f>
+      <c r="M15" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" s="21">
+        <f>SUM(C15,E15,G15,I15,K15,M15)</f>
+        <v/>
+      </c>
+      <c r="P15" s="21">
+        <f>SUM(D15,F15,H15,J15,L15,N15)</f>
         <v/>
       </c>
     </row>
@@ -11387,12 +13621,18 @@
       <c r="J16" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="M16" s="29">
-        <f>SUM(C16,E16,G16,I16,K16)</f>
-        <v/>
-      </c>
-      <c r="N16" s="29">
-        <f>SUM(D16,F16,H16,J16,L16)</f>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16">
+        <f>SUM(C16,E16,G16,I16,K16,M16)</f>
+        <v/>
+      </c>
+      <c r="P16">
+        <f>SUM(D16,F16,H16,J16,L16,N16)</f>
         <v/>
       </c>
     </row>
@@ -11417,12 +13657,18 @@
       <c r="F17" s="29" t="n"/>
       <c r="G17" s="29" t="n"/>
       <c r="H17" s="29" t="n"/>
-      <c r="M17" s="29">
-        <f>SUM(C17,E17,G17,I17,K17)</f>
-        <v/>
-      </c>
-      <c r="N17" s="29">
-        <f>SUM(D17,F17,H17,J17,L17)</f>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O17">
+        <f>SUM(C17,E17,G17,I17,K17,M17)</f>
+        <v/>
+      </c>
+      <c r="P17">
+        <f>SUM(D17,F17,H17,J17,L17,N17)</f>
         <v/>
       </c>
     </row>
@@ -11463,12 +13709,18 @@
       <c r="L18" s="21" t="n">
         <v>-3</v>
       </c>
-      <c r="M18" s="29">
-        <f>SUM(C18,E18,G18,I18,K18)</f>
-        <v/>
-      </c>
-      <c r="N18" s="29">
-        <f>SUM(D18,F18,H18,J18,L18)</f>
+      <c r="M18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="21" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O18" s="21">
+        <f>SUM(C18,E18,G18,I18,K18,M18)</f>
+        <v/>
+      </c>
+      <c r="P18" s="21">
+        <f>SUM(D18,F18,H18,J18,L18,N18)</f>
         <v/>
       </c>
     </row>
@@ -11497,12 +13749,12 @@
       </c>
       <c r="G19" s="32" t="n"/>
       <c r="H19" s="32" t="n"/>
-      <c r="M19" s="32">
-        <f>SUM(C19,E19,G19,I19,K19)</f>
-        <v/>
-      </c>
-      <c r="N19" s="32">
-        <f>SUM(D19,F19,H19,J19,L19)</f>
+      <c r="O19">
+        <f>SUM(C19,E19,G19,I19,K19,M19)</f>
+        <v/>
+      </c>
+      <c r="P19">
+        <f>SUM(D19,F19,H19,J19,L19,N19)</f>
         <v/>
       </c>
     </row>
@@ -11533,12 +13785,14 @@
       <c r="L20" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="M20" s="32">
-        <f>SUM(C20,E20,G20,I20,K20)</f>
-        <v/>
-      </c>
-      <c r="N20" s="32">
-        <f>SUM(D20,F20,H20,J20,L20)</f>
+      <c r="M20" s="21" t="n"/>
+      <c r="N20" s="21" t="n"/>
+      <c r="O20" s="21">
+        <f>SUM(C20,E20,G20,I20,K20,M20)</f>
+        <v/>
+      </c>
+      <c r="P20" s="21">
+        <f>SUM(D20,F20,H20,J20,L20,N20)</f>
         <v/>
       </c>
     </row>
@@ -11565,12 +13819,12 @@
       <c r="J21" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="M21" s="21">
-        <f>SUM(C21,E21,G21,I21,K21)</f>
-        <v/>
-      </c>
-      <c r="N21" s="21">
-        <f>SUM(D21,F21,H21,J21,L21)</f>
+      <c r="O21">
+        <f>SUM(C21,E21,G21,I21,K21,M21)</f>
+        <v/>
+      </c>
+      <c r="P21">
+        <f>SUM(D21,F21,H21,J21,L21,N21)</f>
         <v/>
       </c>
     </row>
@@ -11591,12 +13845,12 @@
       <c r="J22" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="M22" s="21">
-        <f>SUM(C22,E22,G22,I22,K22)</f>
-        <v/>
-      </c>
-      <c r="N22" s="21">
-        <f>SUM(D22,F22,H22,J22,L22)</f>
+      <c r="O22">
+        <f>SUM(C22,E22,G22,I22,K22,M22)</f>
+        <v/>
+      </c>
+      <c r="P22">
+        <f>SUM(D22,F22,H22,J22,L22,N22)</f>
         <v/>
       </c>
     </row>
@@ -11617,12 +13871,12 @@
       <c r="J23" s="21" t="n">
         <v>-1</v>
       </c>
-      <c r="M23" s="21">
-        <f>SUM(C23,E23,G23,I23,K23)</f>
-        <v/>
-      </c>
-      <c r="N23" s="21">
-        <f>SUM(D23,F23,H23,J23,L23)</f>
+      <c r="O23">
+        <f>SUM(C23,E23,G23,I23,K23,M23)</f>
+        <v/>
+      </c>
+      <c r="P23">
+        <f>SUM(D23,F23,H23,J23,L23,N23)</f>
         <v/>
       </c>
     </row>
@@ -11643,12 +13897,14 @@
       <c r="L24" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="21">
-        <f>SUM(C24,E24,G24,I24,K24)</f>
-        <v/>
-      </c>
-      <c r="N24" s="21">
-        <f>SUM(D24,F24,H24,J24,L24)</f>
+      <c r="M24" s="21" t="n"/>
+      <c r="N24" s="21" t="n"/>
+      <c r="O24" s="21">
+        <f>SUM(C24,E24,G24,I24,K24,M24)</f>
+        <v/>
+      </c>
+      <c r="P24" s="21">
+        <f>SUM(D24,F24,H24,J24,L24,N24)</f>
         <v/>
       </c>
     </row>
@@ -11669,12 +13925,14 @@
       <c r="L25" s="21" t="n">
         <v>-3</v>
       </c>
-      <c r="M25" s="21">
-        <f>SUM(C25,E25,G25,I25,K25)</f>
-        <v/>
-      </c>
-      <c r="N25" s="21">
-        <f>SUM(D25,F25,H25,J25,L25)</f>
+      <c r="M25" s="21" t="n"/>
+      <c r="N25" s="21" t="n"/>
+      <c r="O25" s="21">
+        <f>SUM(C25,E25,G25,I25,K25,M25)</f>
+        <v/>
+      </c>
+      <c r="P25" s="21">
+        <f>SUM(D25,F25,H25,J25,L25,N25)</f>
         <v/>
       </c>
     </row>
@@ -11732,6 +13990,14 @@
         <f>SUMIF($B$3:$B$25,"GRIS",N3:N25)</f>
         <v/>
       </c>
+      <c r="O26" s="21">
+        <f>SUMIF($B$3:$B$25,"GRIS",O3:O25)</f>
+        <v/>
+      </c>
+      <c r="P26" s="21">
+        <f>SUMIF($B$3:$B$25,"GRIS",P3:P25)</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="22">
       <c r="A27" s="34" t="inlineStr">
@@ -11785,6 +14051,14 @@
       </c>
       <c r="N27" s="21">
         <f>SUMIF($B$3:$B$25,"ROJO",N3:N25)</f>
+        <v/>
+      </c>
+      <c r="O27" s="21">
+        <f>SUMIF($B$3:$B$25,"ROJO",O3:O25)</f>
+        <v/>
+      </c>
+      <c r="P27" s="21">
+        <f>SUMIF($B$3:$B$25,"ROJO",P3:P25)</f>
         <v/>
       </c>
     </row>
@@ -12517,13 +14791,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="21" min="1" max="1"/>
@@ -12562,12 +14836,17 @@
           <t>F5 Gross</t>
         </is>
       </c>
-      <c r="G1" s="27" t="inlineStr">
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>F6 Gross</t>
+        </is>
+      </c>
+      <c r="H1" s="21" t="inlineStr">
         <is>
           <t>Avg</t>
         </is>
       </c>
-      <c r="H1" s="27" t="inlineStr">
+      <c r="I1" s="21" t="inlineStr">
         <is>
           <t>Mejor</t>
         </is>
@@ -12600,12 +14879,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A2, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G2" s="29">
-        <f>IFERROR(AVERAGE(C2:F2), "")</f>
-        <v/>
-      </c>
-      <c r="H2" s="29">
-        <f>IFERROR(MIN(C2:F2), "")</f>
+      <c r="G2" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A2, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H2" s="21">
+        <f>IFERROR(AVERAGE(C2:G2), "")</f>
+        <v/>
+      </c>
+      <c r="I2" s="21">
+        <f>IFERROR(MIN(C2:G2), "")</f>
         <v/>
       </c>
     </row>
@@ -12636,12 +14919,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A3, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G3" s="29">
-        <f>IFERROR(AVERAGE(C3:F3), "")</f>
-        <v/>
-      </c>
-      <c r="H3" s="29">
-        <f>IFERROR(MIN(C3:F3), "")</f>
+      <c r="G3" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A3, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H3" s="21">
+        <f>IFERROR(AVERAGE(C3:G3), "")</f>
+        <v/>
+      </c>
+      <c r="I3" s="21">
+        <f>IFERROR(MIN(C3:G3), "")</f>
         <v/>
       </c>
     </row>
@@ -12672,12 +14959,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A4, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G4" s="29">
-        <f>IFERROR(AVERAGE(C4:F4), "")</f>
-        <v/>
-      </c>
-      <c r="H4" s="29">
-        <f>IFERROR(MIN(C4:F4), "")</f>
+      <c r="G4" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A4, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H4" s="21">
+        <f>IFERROR(AVERAGE(C4:G4), "")</f>
+        <v/>
+      </c>
+      <c r="I4" s="21">
+        <f>IFERROR(MIN(C4:G4), "")</f>
         <v/>
       </c>
     </row>
@@ -12708,12 +14999,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A5, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G5" s="29">
-        <f>IFERROR(AVERAGE(C5:F5), "")</f>
-        <v/>
-      </c>
-      <c r="H5" s="29">
-        <f>IFERROR(MIN(C5:F5), "")</f>
+      <c r="G5" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A5, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H5" s="21">
+        <f>IFERROR(AVERAGE(C5:G5), "")</f>
+        <v/>
+      </c>
+      <c r="I5" s="21">
+        <f>IFERROR(MIN(C5:G5), "")</f>
         <v/>
       </c>
     </row>
@@ -12744,12 +15039,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A6, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G6" s="29">
-        <f>IFERROR(AVERAGE(C6:F6), "")</f>
-        <v/>
-      </c>
-      <c r="H6" s="29">
-        <f>IFERROR(MIN(C6:F6), "")</f>
+      <c r="G6" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A6, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H6" s="21">
+        <f>IFERROR(AVERAGE(C6:G6), "")</f>
+        <v/>
+      </c>
+      <c r="I6" s="21">
+        <f>IFERROR(MIN(C6:G6), "")</f>
         <v/>
       </c>
     </row>
@@ -12780,12 +15079,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A7, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G7" s="29">
-        <f>IFERROR(AVERAGE(C7:F7), "")</f>
-        <v/>
-      </c>
-      <c r="H7" s="29">
-        <f>IFERROR(MIN(C7:F7), "")</f>
+      <c r="G7" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A7, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H7" s="21">
+        <f>IFERROR(AVERAGE(C7:G7), "")</f>
+        <v/>
+      </c>
+      <c r="I7" s="21">
+        <f>IFERROR(MIN(C7:G7), "")</f>
         <v/>
       </c>
     </row>
@@ -12816,12 +15119,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A8, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G8" s="29">
-        <f>IFERROR(AVERAGE(C8:F8), "")</f>
-        <v/>
-      </c>
-      <c r="H8" s="29">
-        <f>IFERROR(MIN(C8:F8), "")</f>
+      <c r="G8" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A8, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H8" s="21">
+        <f>IFERROR(AVERAGE(C8:G8), "")</f>
+        <v/>
+      </c>
+      <c r="I8" s="21">
+        <f>IFERROR(MIN(C8:G8), "")</f>
         <v/>
       </c>
     </row>
@@ -12852,12 +15159,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A9, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G9" s="29">
-        <f>IFERROR(AVERAGE(C9:F9), "")</f>
-        <v/>
-      </c>
-      <c r="H9" s="29">
-        <f>IFERROR(MIN(C9:F9), "")</f>
+      <c r="G9" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A9, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H9" s="21">
+        <f>IFERROR(AVERAGE(C9:G9), "")</f>
+        <v/>
+      </c>
+      <c r="I9" s="21">
+        <f>IFERROR(MIN(C9:G9), "")</f>
         <v/>
       </c>
     </row>
@@ -12888,12 +15199,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A10, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G10" s="29">
-        <f>IFERROR(AVERAGE(C10:F10), "")</f>
-        <v/>
-      </c>
-      <c r="H10" s="29">
-        <f>IFERROR(MIN(C10:F10), "")</f>
+      <c r="G10" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A10, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H10" s="21">
+        <f>IFERROR(AVERAGE(C10:G10), "")</f>
+        <v/>
+      </c>
+      <c r="I10" s="21">
+        <f>IFERROR(MIN(C10:G10), "")</f>
         <v/>
       </c>
     </row>
@@ -12924,12 +15239,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A11, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G11" s="29">
-        <f>IFERROR(AVERAGE(C11:F11), "")</f>
-        <v/>
-      </c>
-      <c r="H11" s="29">
-        <f>IFERROR(MIN(C11:F11), "")</f>
+      <c r="G11" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A11, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H11" s="21">
+        <f>IFERROR(AVERAGE(C11:G11), "")</f>
+        <v/>
+      </c>
+      <c r="I11" s="21">
+        <f>IFERROR(MIN(C11:G11), "")</f>
         <v/>
       </c>
     </row>
@@ -12960,12 +15279,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A12, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G12" s="29">
-        <f>IFERROR(AVERAGE(C12:F12), "")</f>
-        <v/>
-      </c>
-      <c r="H12" s="29">
-        <f>IFERROR(MIN(C12:F12), "")</f>
+      <c r="G12" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A12, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H12" s="21">
+        <f>IFERROR(AVERAGE(C12:G12), "")</f>
+        <v/>
+      </c>
+      <c r="I12" s="21">
+        <f>IFERROR(MIN(C12:G12), "")</f>
         <v/>
       </c>
     </row>
@@ -12996,12 +15319,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A13, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G13" s="29">
-        <f>IFERROR(AVERAGE(C13:F13), "")</f>
-        <v/>
-      </c>
-      <c r="H13" s="29">
-        <f>IFERROR(MIN(C13:F13), "")</f>
+      <c r="G13" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A13, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H13" s="21">
+        <f>IFERROR(AVERAGE(C13:G13), "")</f>
+        <v/>
+      </c>
+      <c r="I13" s="21">
+        <f>IFERROR(MIN(C13:G13), "")</f>
         <v/>
       </c>
     </row>
@@ -13032,12 +15359,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A14, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G14" s="29">
-        <f>IFERROR(AVERAGE(C14:F14), "")</f>
-        <v/>
-      </c>
-      <c r="H14" s="29">
-        <f>IFERROR(MIN(C14:F14), "")</f>
+      <c r="G14" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A14, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H14" s="21">
+        <f>IFERROR(AVERAGE(C14:G14), "")</f>
+        <v/>
+      </c>
+      <c r="I14" s="21">
+        <f>IFERROR(MIN(C14:G14), "")</f>
         <v/>
       </c>
     </row>
@@ -13068,12 +15399,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A15, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G15" s="29">
-        <f>IFERROR(AVERAGE(C15:F15), "")</f>
-        <v/>
-      </c>
-      <c r="H15" s="29">
-        <f>IFERROR(MIN(C15:F15), "")</f>
+      <c r="G15" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A15, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H15" s="21">
+        <f>IFERROR(AVERAGE(C15:G15), "")</f>
+        <v/>
+      </c>
+      <c r="I15" s="21">
+        <f>IFERROR(MIN(C15:G15), "")</f>
         <v/>
       </c>
     </row>
@@ -13104,12 +15439,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A16, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G16" s="29">
-        <f>IFERROR(AVERAGE(C16:F16), "")</f>
-        <v/>
-      </c>
-      <c r="H16" s="29">
-        <f>IFERROR(MIN(C16:F16), "")</f>
+      <c r="G16" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A16, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H16" s="21">
+        <f>IFERROR(AVERAGE(C16:G16), "")</f>
+        <v/>
+      </c>
+      <c r="I16" s="21">
+        <f>IFERROR(MIN(C16:G16), "")</f>
         <v/>
       </c>
     </row>
@@ -13140,12 +15479,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A17, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G17" s="29">
-        <f>IFERROR(AVERAGE(C17:F17), "")</f>
-        <v/>
-      </c>
-      <c r="H17" s="29">
-        <f>IFERROR(MIN(C17:F17), "")</f>
+      <c r="G17" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A17, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H17" s="21">
+        <f>IFERROR(AVERAGE(C17:G17), "")</f>
+        <v/>
+      </c>
+      <c r="I17" s="21">
+        <f>IFERROR(MIN(C17:G17), "")</f>
         <v/>
       </c>
     </row>
@@ -13176,12 +15519,16 @@
         <f>IFERROR(INDEX('F5'!U:U, MATCH(A18, 'F5'!A:A, 0)), "")</f>
         <v/>
       </c>
-      <c r="G18" s="32">
-        <f>IFERROR(AVERAGE(C18:F18), "")</f>
-        <v/>
-      </c>
-      <c r="H18" s="32">
-        <f>IFERROR(MIN(C18:F18), "")</f>
+      <c r="G18" s="21">
+        <f>IFERROR(INDEX('F6'!U:U, MATCH(A18, 'F6'!A:A, 0)), "")</f>
+        <v/>
+      </c>
+      <c r="H18" s="21">
+        <f>IFERROR(AVERAGE(C18:G18), "")</f>
+        <v/>
+      </c>
+      <c r="I18" s="21">
+        <f>IFERROR(MIN(C18:G18), "")</f>
         <v/>
       </c>
     </row>
@@ -13192,7 +15539,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13464,13 +15811,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="21" min="1" max="1"/>
@@ -13549,6 +15896,21 @@
           <t>F5 Pts</t>
         </is>
       </c>
+      <c r="O1" s="21" t="inlineStr">
+        <is>
+          <t>F6 Neto</t>
+        </is>
+      </c>
+      <c r="P1" s="21" t="inlineStr">
+        <is>
+          <t>F6 Pos</t>
+        </is>
+      </c>
+      <c r="Q1" s="21" t="inlineStr">
+        <is>
+          <t>F6 Pts</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="22">
       <c r="A2" s="28" t="inlineStr">
@@ -13585,6 +15947,15 @@
       <c r="N2" s="21" t="n">
         <v>45</v>
       </c>
+      <c r="O2" s="21" t="n">
+        <v>76</v>
+      </c>
+      <c r="P2" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q2" s="21" t="n">
+        <v>156.67</v>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="22">
       <c r="A3" s="28" t="inlineStr">
@@ -13632,6 +16003,15 @@
       </c>
       <c r="N3" s="21" t="n">
         <v>85</v>
+      </c>
+      <c r="O3" s="21" t="n">
+        <v>77</v>
+      </c>
+      <c r="P3" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q3" s="21" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="22">
@@ -13702,6 +16082,15 @@
       <c r="N5" s="21" t="n">
         <v>156.67</v>
       </c>
+      <c r="O5" s="21" t="n">
+        <v>82</v>
+      </c>
+      <c r="P5" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="21" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="22">
       <c r="A6" s="28" t="inlineStr">
@@ -13741,6 +16130,15 @@
       <c r="K6" s="29" t="n">
         <v>200</v>
       </c>
+      <c r="O6" t="n">
+        <v>79</v>
+      </c>
+      <c r="P6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>77.5</v>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="22">
       <c r="A7" s="28" t="inlineStr">
@@ -13789,6 +16187,15 @@
       <c r="N7" s="21" t="n">
         <v>100</v>
       </c>
+      <c r="O7" s="21" t="n">
+        <v>69</v>
+      </c>
+      <c r="P7" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="21" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="22">
       <c r="A8" s="28" t="inlineStr">
@@ -13837,6 +16244,15 @@
       <c r="N8" s="21" t="n">
         <v>156.67</v>
       </c>
+      <c r="O8" s="21" t="n">
+        <v>76</v>
+      </c>
+      <c r="P8" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="21" t="n">
+        <v>156.67</v>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="22">
       <c r="A9" s="28" t="inlineStr">
@@ -13885,6 +16301,15 @@
       <c r="N9" s="21" t="n">
         <v>20</v>
       </c>
+      <c r="O9" s="21" t="n">
+        <v>83</v>
+      </c>
+      <c r="P9" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q9" s="21" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="22">
       <c r="A10" s="28" t="inlineStr">
@@ -13933,6 +16358,9 @@
       <c r="N10" s="21" t="n">
         <v>156.67</v>
       </c>
+      <c r="O10" s="21" t="n"/>
+      <c r="P10" s="21" t="n"/>
+      <c r="Q10" s="21" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="22">
       <c r="A11" s="28" t="inlineStr">
@@ -13981,6 +16409,15 @@
       <c r="N11" s="21" t="n">
         <v>500</v>
       </c>
+      <c r="O11" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="P11" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="21" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="22">
       <c r="A12" s="28" t="inlineStr">
@@ -14029,6 +16466,15 @@
       <c r="N12" s="21" t="n">
         <v>45</v>
       </c>
+      <c r="O12" s="21" t="n">
+        <v>79</v>
+      </c>
+      <c r="P12" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="21" t="n">
+        <v>77.5</v>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="22">
       <c r="A13" s="28" t="inlineStr">
@@ -14077,6 +16523,15 @@
       <c r="N13" s="21" t="n">
         <v>300</v>
       </c>
+      <c r="O13" s="21" t="n">
+        <v>78</v>
+      </c>
+      <c r="P13" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="21" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="22">
       <c r="A14" s="28" t="inlineStr">
@@ -14116,6 +16571,15 @@
       <c r="K14" s="29" t="n">
         <v>20</v>
       </c>
+      <c r="O14" t="n">
+        <v>76</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>156.67</v>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="22">
       <c r="A15" s="28" t="inlineStr">
@@ -14154,6 +16618,15 @@
       </c>
       <c r="K15" s="29" t="n">
         <v>36.67</v>
+      </c>
+      <c r="O15" t="n">
+        <v>80</v>
+      </c>
+      <c r="P15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="22">
@@ -14214,6 +16687,15 @@
       </c>
       <c r="K17" s="29" t="n">
         <v>500</v>
+      </c>
+      <c r="O17" t="n">
+        <v>80</v>
+      </c>
+      <c r="P17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="22">
@@ -14290,6 +16772,9 @@
       <c r="N19" s="21" t="n">
         <v>75</v>
       </c>
+      <c r="O19" s="21" t="n"/>
+      <c r="P19" s="21" t="n"/>
+      <c r="Q19" s="21" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="22">
       <c r="A20" s="31" t="inlineStr">
@@ -14332,608 +16817,9 @@
       <c r="N21" s="21" t="n">
         <v>85</v>
       </c>
-    </row>
-  </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="24" customWidth="1" style="21" min="1" max="1"/>
-    <col width="8" customWidth="1" style="21" min="2" max="2"/>
-    <col width="11" customWidth="1" style="21" min="3" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="21.75" customHeight="1" s="22">
-      <c r="A1" s="27" t="inlineStr">
-        <is>
-          <t>Jugador</t>
-        </is>
-      </c>
-      <c r="B1" s="27" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-      <c r="C1" s="27" t="inlineStr">
-        <is>
-          <t>F1 Pts</t>
-        </is>
-      </c>
-      <c r="D1" s="27" t="inlineStr">
-        <is>
-          <t>F2 Pts</t>
-        </is>
-      </c>
-      <c r="E1" s="27" t="inlineStr">
-        <is>
-          <t>F3 Pts</t>
-        </is>
-      </c>
-      <c r="F1" s="21" t="inlineStr">
-        <is>
-          <t>F5 Pts</t>
-        </is>
-      </c>
-      <c r="G1" s="27" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="22">
-      <c r="A2" s="28" t="inlineStr">
-        <is>
-          <t>Fernandez, Lucas</t>
-        </is>
-      </c>
-      <c r="B2" s="28" t="inlineStr">
-        <is>
-          <t>ROJO</t>
-        </is>
-      </c>
-      <c r="C2" s="29">
-        <f>IFERROR(VLOOKUP(A2, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D2" s="29">
-        <f>IFERROR(VLOOKUP(A2, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E2" s="29">
-        <f>IFERROR(VLOOKUP(A2, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F2" s="21">
-        <f>IFERROR(VLOOKUP(A2, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G2" s="29">
-        <f>SUM(C2:F2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="22">
-      <c r="A3" s="28" t="inlineStr">
-        <is>
-          <t>Gatto, Mariano</t>
-        </is>
-      </c>
-      <c r="B3" s="28" t="inlineStr">
-        <is>
-          <t>ROJO</t>
-        </is>
-      </c>
-      <c r="C3" s="29">
-        <f>IFERROR(VLOOKUP(A3, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D3" s="29">
-        <f>IFERROR(VLOOKUP(A3, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E3" s="29">
-        <f>IFERROR(VLOOKUP(A3, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F3" s="21">
-        <f>IFERROR(VLOOKUP(A3, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G3" s="29">
-        <f>SUM(C3:F3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="22">
-      <c r="A4" s="28" t="inlineStr">
-        <is>
-          <t>Guevara, Franki</t>
-        </is>
-      </c>
-      <c r="B4" s="28" t="inlineStr">
-        <is>
-          <t>GRIS</t>
-        </is>
-      </c>
-      <c r="C4" s="29">
-        <f>IFERROR(VLOOKUP(A4, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="29">
-        <f>IFERROR(VLOOKUP(A4, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="29">
-        <f>IFERROR(VLOOKUP(A4, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="21">
-        <f>IFERROR(VLOOKUP(A4, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="29">
-        <f>SUM(C4:F4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="22">
-      <c r="A5" s="28" t="inlineStr">
-        <is>
-          <t>Vogelius, Nico</t>
-        </is>
-      </c>
-      <c r="B5" s="28" t="inlineStr">
-        <is>
-          <t>ROJO</t>
-        </is>
-      </c>
-      <c r="C5" s="29">
-        <f>IFERROR(VLOOKUP(A5, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D5" s="29">
-        <f>IFERROR(VLOOKUP(A5, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E5" s="29">
-        <f>IFERROR(VLOOKUP(A5, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F5" s="21">
-        <f>IFERROR(VLOOKUP(A5, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G5" s="29">
-        <f>SUM(C5:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="22">
-      <c r="A6" s="28" t="inlineStr">
-        <is>
-          <t>Elizalde, Juancho</t>
-        </is>
-      </c>
-      <c r="B6" s="28" t="inlineStr">
-        <is>
-          <t>ROJO</t>
-        </is>
-      </c>
-      <c r="C6" s="29">
-        <f>IFERROR(VLOOKUP(A6, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="29">
-        <f>IFERROR(VLOOKUP(A6, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E6" s="29">
-        <f>IFERROR(VLOOKUP(A6, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F6" s="21">
-        <f>IFERROR(VLOOKUP(A6, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="29">
-        <f>SUM(C6:F6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="22">
-      <c r="A7" s="28" t="inlineStr">
-        <is>
-          <t>Tarasido, Gonzalo</t>
-        </is>
-      </c>
-      <c r="B7" s="28" t="inlineStr">
-        <is>
-          <t>GRIS</t>
-        </is>
-      </c>
-      <c r="C7" s="29">
-        <f>IFERROR(VLOOKUP(A7, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="29">
-        <f>IFERROR(VLOOKUP(A7, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E7" s="29">
-        <f>IFERROR(VLOOKUP(A7, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="21">
-        <f>IFERROR(VLOOKUP(A7, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="29">
-        <f>SUM(C7:F7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="22">
-      <c r="A8" s="28" t="inlineStr">
-        <is>
-          <t>Pannullo, Tincho</t>
-        </is>
-      </c>
-      <c r="B8" s="28" t="inlineStr">
-        <is>
-          <t>GRIS</t>
-        </is>
-      </c>
-      <c r="C8" s="29">
-        <f>IFERROR(VLOOKUP(A8, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="29">
-        <f>IFERROR(VLOOKUP(A8, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E8" s="29">
-        <f>IFERROR(VLOOKUP(A8, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="21">
-        <f>IFERROR(VLOOKUP(A8, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="29">
-        <f>SUM(C8:F8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="22">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>Molinario, Andy</t>
-        </is>
-      </c>
-      <c r="B9" s="28" t="inlineStr">
-        <is>
-          <t>ROJO</t>
-        </is>
-      </c>
-      <c r="C9" s="29">
-        <f>IFERROR(VLOOKUP(A9, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="29">
-        <f>IFERROR(VLOOKUP(A9, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E9" s="29">
-        <f>IFERROR(VLOOKUP(A9, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="21">
-        <f>IFERROR(VLOOKUP(A9, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="29">
-        <f>SUM(C9:F9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="22">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>Mendez, Pato</t>
-        </is>
-      </c>
-      <c r="B10" s="28" t="inlineStr">
-        <is>
-          <t>ROJO</t>
-        </is>
-      </c>
-      <c r="C10" s="29">
-        <f>IFERROR(VLOOKUP(A10, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D10" s="29">
-        <f>IFERROR(VLOOKUP(A10, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E10" s="29">
-        <f>IFERROR(VLOOKUP(A10, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F10" s="21">
-        <f>IFERROR(VLOOKUP(A10, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="29">
-        <f>SUM(C10:F10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="22">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>Dipaola, Martin</t>
-        </is>
-      </c>
-      <c r="B11" s="28" t="inlineStr">
-        <is>
-          <t>GRIS</t>
-        </is>
-      </c>
-      <c r="C11" s="29">
-        <f>IFERROR(VLOOKUP(A11, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="29">
-        <f>IFERROR(VLOOKUP(A11, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E11" s="29">
-        <f>IFERROR(VLOOKUP(A11, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F11" s="21">
-        <f>IFERROR(VLOOKUP(A11, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="29">
-        <f>SUM(C11:F11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="22">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>Benegas, Pancho</t>
-        </is>
-      </c>
-      <c r="B12" s="28" t="inlineStr">
-        <is>
-          <t>GRIS</t>
-        </is>
-      </c>
-      <c r="C12" s="29">
-        <f>IFERROR(VLOOKUP(A12, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="29">
-        <f>IFERROR(VLOOKUP(A12, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E12" s="29">
-        <f>IFERROR(VLOOKUP(A12, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F12" s="21">
-        <f>IFERROR(VLOOKUP(A12, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G12" s="29">
-        <f>SUM(C12:F12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="22">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>Canónico, Agus</t>
-        </is>
-      </c>
-      <c r="B13" s="28" t="inlineStr">
-        <is>
-          <t>ROJO</t>
-        </is>
-      </c>
-      <c r="C13" s="29">
-        <f>IFERROR(VLOOKUP(A13, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="29">
-        <f>IFERROR(VLOOKUP(A13, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E13" s="29">
-        <f>IFERROR(VLOOKUP(A13, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F13" s="21">
-        <f>IFERROR(VLOOKUP(A13, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G13" s="29">
-        <f>SUM(C13:F13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="22">
-      <c r="A14" s="28" t="inlineStr">
-        <is>
-          <t>Basaldua, Ignacio</t>
-        </is>
-      </c>
-      <c r="B14" s="28" t="inlineStr">
-        <is>
-          <t>GRIS</t>
-        </is>
-      </c>
-      <c r="C14" s="29">
-        <f>IFERROR(VLOOKUP(A14, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D14" s="29">
-        <f>IFERROR(VLOOKUP(A14, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E14" s="29">
-        <f>IFERROR(VLOOKUP(A14, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F14" s="21">
-        <f>IFERROR(VLOOKUP(A14, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G14" s="29">
-        <f>SUM(C14:F14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="22">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>Zunino, Javi</t>
-        </is>
-      </c>
-      <c r="B15" s="28" t="inlineStr">
-        <is>
-          <t>GRIS</t>
-        </is>
-      </c>
-      <c r="C15" s="29">
-        <f>IFERROR(VLOOKUP(A15, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D15" s="29">
-        <f>IFERROR(VLOOKUP(A15, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E15" s="29">
-        <f>IFERROR(VLOOKUP(A15, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F15" s="21">
-        <f>IFERROR(VLOOKUP(A15, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G15" s="29">
-        <f>SUM(C15:F15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="22">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>Scapparone, Nico</t>
-        </is>
-      </c>
-      <c r="B16" s="28" t="inlineStr">
-        <is>
-          <t>ROJO</t>
-        </is>
-      </c>
-      <c r="C16" s="29">
-        <f>IFERROR(VLOOKUP(A16, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="29">
-        <f>IFERROR(VLOOKUP(A16, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E16" s="29">
-        <f>IFERROR(VLOOKUP(A16, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F16" s="21">
-        <f>IFERROR(VLOOKUP(A16, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G16" s="29">
-        <f>SUM(C16:F16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="22">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>Gonzalez, Agus</t>
-        </is>
-      </c>
-      <c r="B17" s="28" t="inlineStr">
-        <is>
-          <t>GRIS</t>
-        </is>
-      </c>
-      <c r="C17" s="29">
-        <f>IFERROR(VLOOKUP(A17, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="29">
-        <f>IFERROR(VLOOKUP(A17, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E17" s="29">
-        <f>IFERROR(VLOOKUP(A17, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F17" s="21">
-        <f>IFERROR(VLOOKUP(A17, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G17" s="29">
-        <f>SUM(C17:F17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="22">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>Gatto, Alejandro</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C18" s="32">
-        <f>IFERROR(VLOOKUP(A18, Medal_Fechas!$A:$K, 5, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="D18" s="32">
-        <f>IFERROR(VLOOKUP(A18, Medal_Fechas!$A:$K, 8, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="E18" s="32">
-        <f>IFERROR(VLOOKUP(A18, Medal_Fechas!$A:$K, 11, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="F18" s="21">
-        <f>IFERROR(VLOOKUP(A18, Medal_Fechas!$A:$N, 14, FALSE()), 0)</f>
-        <v/>
-      </c>
-      <c r="G18" s="32">
-        <f>SUM(C18:F18)</f>
-        <v/>
-      </c>
+      <c r="O21" s="21" t="n"/>
+      <c r="P21" s="21" t="n"/>
+      <c r="Q21" s="21" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
